--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16.48592535154322</v>
+        <v>14.30639691065161</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15.28890734429548</v>
+        <v>12.93279399911269</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19.27896736845461</v>
+        <v>17.5114703709091</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>148415.0863297456</v>
+        <v>315443.8661644891</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9575166859983586</v>
+        <v>2.035121717190252</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2729.896666666667</v>
+        <v>2350.464316600884</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>2462.150666666666</v>
+        <v>2082.718316600884</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15.28890734429548</v>
+        <v>12.93279399911269</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15.28890734429548</v>
+        <v>12.93279399911269</v>
       </c>
     </row>
     <row r="13">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>13.37534942386774</v>
+        <v>11.14005164280475</v>
       </c>
       <c r="F11" t="n">
-        <v>10.57617027498051</v>
+        <v>8.808673277435005</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>19.27896736845461</v>
+        <v>17.5114703709091</v>
       </c>
     </row>
     <row r="13">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.79249694494133</v>
+        <v>11.04887419222804</v>
       </c>
       <c r="C2" t="n">
-        <v>14.3358260890874</v>
+        <v>12.37425049228495</v>
       </c>
       <c r="D2" t="n">
-        <v>15.87915523323347</v>
+        <v>13.69962679234186</v>
       </c>
       <c r="E2" t="n">
-        <v>17.42248437737954</v>
+        <v>15.02500309239877</v>
       </c>
       <c r="F2" t="n">
-        <v>18.96581352152561</v>
+        <v>16.35037939245568</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13.0958820040962</v>
+        <v>11.35225925138291</v>
       </c>
       <c r="C3" t="n">
-        <v>14.63921114824227</v>
+        <v>12.67763555143982</v>
       </c>
       <c r="D3" t="n">
-        <v>16.18254029238834</v>
+        <v>14.00301185149674</v>
       </c>
       <c r="E3" t="n">
-        <v>17.72586943653442</v>
+        <v>15.32838815155365</v>
       </c>
       <c r="F3" t="n">
-        <v>19.26919858068049</v>
+        <v>16.65376445161056</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.39926706325107</v>
+        <v>11.65564431053779</v>
       </c>
       <c r="C4" t="n">
-        <v>14.94259620739715</v>
+        <v>12.9810206105947</v>
       </c>
       <c r="D4" t="n">
-        <v>16.48592535154322</v>
+        <v>14.30639691065161</v>
       </c>
       <c r="E4" t="n">
-        <v>18.02925449568929</v>
+        <v>15.63177321070852</v>
       </c>
       <c r="F4" t="n">
-        <v>19.57258363983536</v>
+        <v>16.95714951076543</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.70265212240595</v>
+        <v>11.95902936969266</v>
       </c>
       <c r="C5" t="n">
-        <v>15.24598126655202</v>
+        <v>13.28440566974957</v>
       </c>
       <c r="D5" t="n">
-        <v>16.78931041069809</v>
+        <v>14.60978196980648</v>
       </c>
       <c r="E5" t="n">
-        <v>18.33263955484416</v>
+        <v>15.93515826986339</v>
       </c>
       <c r="F5" t="n">
-        <v>19.87596869899023</v>
+        <v>17.2605345699203</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14.00603718156082</v>
+        <v>12.26241442884753</v>
       </c>
       <c r="C6" t="n">
-        <v>15.54936632570689</v>
+        <v>13.58779072890444</v>
       </c>
       <c r="D6" t="n">
-        <v>17.09269546985296</v>
+        <v>14.91316702896136</v>
       </c>
       <c r="E6" t="n">
-        <v>18.63602461399904</v>
+        <v>16.23854332901826</v>
       </c>
       <c r="F6" t="n">
-        <v>20.1793537581451</v>
+        <v>17.56391962907517</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.96</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>16.36</v>
+        <v>14.18</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>16.49</v>
+        <v>14.31</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>315443.8661644891</v>
+        <v>330770.9228526246</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.035121717190252</v>
+        <v>2.1340059538879</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.6</v>
+        <v>16.925</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>330770.9228526246</v>
+        <v>355677.3899708443</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1340059538879</v>
+        <v>2.294692838521576</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.925</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>355677.3899708443</v>
+        <v>334602.6870246581</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.294692838521576</v>
+        <v>2.15872701306231</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.65</v>
+        <v>18.89</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>334602.6870246581</v>
+        <v>506265.721931773</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.15872701306231</v>
+        <v>3.266230464075955</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.30639691065161</v>
+        <v>14.00269739696556</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.5114703709091</v>
+        <v>16.49913865862225</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>506265.721931773</v>
+        <v>529539.8202438992</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.266230464075955</v>
+        <v>3.416385937057415</v>
       </c>
     </row>
   </sheetData>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>11.14005164280475</v>
+        <v>9.859787612191461</v>
       </c>
       <c r="F11" t="n">
-        <v>8.808673277435005</v>
+        <v>7.796341565148154</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17.5114703709091</v>
+        <v>16.49913865862225</v>
       </c>
     </row>
     <row r="13">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.04887419222804</v>
+        <v>10.8059145812792</v>
       </c>
       <c r="C2" t="n">
-        <v>12.37425049228495</v>
+        <v>12.1009209299675</v>
       </c>
       <c r="D2" t="n">
-        <v>13.69962679234186</v>
+        <v>13.39592727865581</v>
       </c>
       <c r="E2" t="n">
-        <v>15.02500309239877</v>
+        <v>14.69093362734411</v>
       </c>
       <c r="F2" t="n">
-        <v>16.35037939245568</v>
+        <v>15.98593997603241</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.35225925138291</v>
+        <v>11.10929964043407</v>
       </c>
       <c r="C3" t="n">
-        <v>12.67763555143982</v>
+        <v>12.40430598912237</v>
       </c>
       <c r="D3" t="n">
-        <v>14.00301185149674</v>
+        <v>13.69931233781068</v>
       </c>
       <c r="E3" t="n">
-        <v>15.32838815155365</v>
+        <v>14.99431868649899</v>
       </c>
       <c r="F3" t="n">
-        <v>16.65376445161056</v>
+        <v>16.28932503518729</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.65564431053779</v>
+        <v>11.41268469958894</v>
       </c>
       <c r="C4" t="n">
-        <v>12.9810206105947</v>
+        <v>12.70769104827725</v>
       </c>
       <c r="D4" t="n">
-        <v>14.30639691065161</v>
+        <v>14.00269739696556</v>
       </c>
       <c r="E4" t="n">
-        <v>15.63177321070852</v>
+        <v>15.29770374565386</v>
       </c>
       <c r="F4" t="n">
-        <v>16.95714951076543</v>
+        <v>16.59271009434216</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.95902936969266</v>
+        <v>11.71606975874382</v>
       </c>
       <c r="C5" t="n">
-        <v>13.28440566974957</v>
+        <v>13.01107610743212</v>
       </c>
       <c r="D5" t="n">
-        <v>14.60978196980648</v>
+        <v>14.30608245612043</v>
       </c>
       <c r="E5" t="n">
-        <v>15.93515826986339</v>
+        <v>15.60108880480873</v>
       </c>
       <c r="F5" t="n">
-        <v>17.2605345699203</v>
+        <v>16.89609515349703</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.26241442884753</v>
+        <v>12.01945481789869</v>
       </c>
       <c r="C6" t="n">
-        <v>13.58779072890444</v>
+        <v>13.31446116658699</v>
       </c>
       <c r="D6" t="n">
-        <v>14.91316702896136</v>
+        <v>14.6094675152753</v>
       </c>
       <c r="E6" t="n">
-        <v>16.23854332901826</v>
+        <v>15.9044738639636</v>
       </c>
       <c r="F6" t="n">
-        <v>17.56391962907517</v>
+        <v>17.19948021265191</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>13.78</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>14.18</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>14.31</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.00269739696556</v>
+        <v>14.15166907441216</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.93279399911269</v>
+        <v>13.09525884704837</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.49913865862225</v>
+        <v>16.61662627159434</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>529539.8202438992</v>
+        <v>518123.333518146</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.416385937057415</v>
+        <v>3.342731183988039</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2350.464316600884</v>
+        <v>2376.627921667401</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>2082.718316600884</v>
+        <v>2108.881921667401</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12.93279399911269</v>
+        <v>13.09525884704837</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12.93279399911269</v>
+        <v>13.09525884704837</v>
       </c>
     </row>
     <row r="13">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.859787612191461</v>
+        <v>10.00837049575144</v>
       </c>
       <c r="F11" t="n">
-        <v>7.796341565148154</v>
+        <v>7.913829178120249</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16.49913865862225</v>
+        <v>16.61662627159434</v>
       </c>
     </row>
     <row r="13">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.8059145812792</v>
+        <v>10.92509192323648</v>
       </c>
       <c r="C2" t="n">
-        <v>12.1009209299675</v>
+        <v>12.23499543966945</v>
       </c>
       <c r="D2" t="n">
-        <v>13.39592727865581</v>
+        <v>13.54489895610241</v>
       </c>
       <c r="E2" t="n">
-        <v>14.69093362734411</v>
+        <v>14.85480247253538</v>
       </c>
       <c r="F2" t="n">
-        <v>15.98593997603241</v>
+        <v>16.16470598896834</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.10929964043407</v>
+        <v>11.22847698239135</v>
       </c>
       <c r="C3" t="n">
-        <v>12.40430598912237</v>
+        <v>12.53838049882432</v>
       </c>
       <c r="D3" t="n">
-        <v>13.69931233781068</v>
+        <v>13.84828401525728</v>
       </c>
       <c r="E3" t="n">
-        <v>14.99431868649899</v>
+        <v>15.15818753169025</v>
       </c>
       <c r="F3" t="n">
-        <v>16.28932503518729</v>
+        <v>16.46809104812321</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.41268469958894</v>
+        <v>11.53186204154622</v>
       </c>
       <c r="C4" t="n">
-        <v>12.70769104827725</v>
+        <v>12.84176555797919</v>
       </c>
       <c r="D4" t="n">
-        <v>14.00269739696556</v>
+        <v>14.15166907441216</v>
       </c>
       <c r="E4" t="n">
-        <v>15.29770374565386</v>
+        <v>15.46157259084513</v>
       </c>
       <c r="F4" t="n">
-        <v>16.59271009434216</v>
+        <v>16.77147610727809</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.71606975874382</v>
+        <v>11.8352471007011</v>
       </c>
       <c r="C5" t="n">
-        <v>13.01107610743212</v>
+        <v>13.14515061713407</v>
       </c>
       <c r="D5" t="n">
-        <v>14.30608245612043</v>
+        <v>14.45505413356703</v>
       </c>
       <c r="E5" t="n">
-        <v>15.60108880480873</v>
+        <v>15.76495765</v>
       </c>
       <c r="F5" t="n">
-        <v>16.89609515349703</v>
+        <v>17.07486116643296</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.01945481789869</v>
+        <v>12.13863215985597</v>
       </c>
       <c r="C6" t="n">
-        <v>13.31446116658699</v>
+        <v>13.44853567628894</v>
       </c>
       <c r="D6" t="n">
-        <v>14.6094675152753</v>
+        <v>14.7584391927219</v>
       </c>
       <c r="E6" t="n">
-        <v>15.9044738639636</v>
+        <v>16.06834270915487</v>
       </c>
       <c r="F6" t="n">
-        <v>17.19948021265191</v>
+        <v>17.37824622558783</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>13.94</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>13.99</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>14.15</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.89</v>
+        <v>17.65</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>518123.333518146</v>
+        <v>423095.5820517073</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.342731183988039</v>
+        <v>2.729648916462628</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.15166907441216</v>
+        <v>13.672001905442</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.09525884704837</v>
+        <v>12.50845408176894</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.61662627159434</v>
+        <v>16.38694682734582</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>423095.5820517073</v>
+        <v>459855.0115029219</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.729648916462628</v>
+        <v>2.966806525825302</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2376.627921667401</v>
+        <v>2282.127921667401</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>2108.881921667401</v>
+        <v>2014.381921667401</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.09525884704837</v>
+        <v>12.50845408176894</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.09525884704837</v>
+        <v>12.50845408176894</v>
       </c>
     </row>
     <row r="13">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.00837049575144</v>
+        <v>9.71790213693812</v>
       </c>
       <c r="F11" t="n">
-        <v>7.913829178120249</v>
+        <v>7.684149733871723</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16.61662627159434</v>
+        <v>16.38694682734582</v>
       </c>
     </row>
     <row r="13">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.92509192323648</v>
+        <v>10.54135818806035</v>
       </c>
       <c r="C2" t="n">
-        <v>12.23499543966945</v>
+        <v>11.8032949875963</v>
       </c>
       <c r="D2" t="n">
-        <v>13.54489895610241</v>
+        <v>13.06523178713226</v>
       </c>
       <c r="E2" t="n">
-        <v>14.85480247253538</v>
+        <v>14.32716858666821</v>
       </c>
       <c r="F2" t="n">
-        <v>16.16470598896834</v>
+        <v>15.58910538620415</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.22847698239135</v>
+        <v>10.84474324721523</v>
       </c>
       <c r="C3" t="n">
-        <v>12.53838049882432</v>
+        <v>12.10668004675118</v>
       </c>
       <c r="D3" t="n">
-        <v>13.84828401525728</v>
+        <v>13.36861684628713</v>
       </c>
       <c r="E3" t="n">
-        <v>15.15818753169025</v>
+        <v>14.63055364582308</v>
       </c>
       <c r="F3" t="n">
-        <v>16.46809104812321</v>
+        <v>15.89249044535902</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.53186204154622</v>
+        <v>11.1481283063701</v>
       </c>
       <c r="C4" t="n">
-        <v>12.84176555797919</v>
+        <v>12.41006510590605</v>
       </c>
       <c r="D4" t="n">
-        <v>14.15166907441216</v>
+        <v>13.672001905442</v>
       </c>
       <c r="E4" t="n">
-        <v>15.46157259084513</v>
+        <v>14.93393870497795</v>
       </c>
       <c r="F4" t="n">
-        <v>16.77147610727809</v>
+        <v>16.1958755045139</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.8352471007011</v>
+        <v>11.45151336552497</v>
       </c>
       <c r="C5" t="n">
-        <v>13.14515061713407</v>
+        <v>12.71345016506092</v>
       </c>
       <c r="D5" t="n">
-        <v>14.45505413356703</v>
+        <v>13.97538696459687</v>
       </c>
       <c r="E5" t="n">
-        <v>15.76495765</v>
+        <v>15.23732376413282</v>
       </c>
       <c r="F5" t="n">
-        <v>17.07486116643296</v>
+        <v>16.49926056366877</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.13863215985597</v>
+        <v>11.75489842467984</v>
       </c>
       <c r="C6" t="n">
-        <v>13.44853567628894</v>
+        <v>13.0168352242158</v>
       </c>
       <c r="D6" t="n">
-        <v>14.7584391927219</v>
+        <v>14.27877202375175</v>
       </c>
       <c r="E6" t="n">
-        <v>16.06834270915487</v>
+        <v>15.5407088232877</v>
       </c>
       <c r="F6" t="n">
-        <v>17.37824622558783</v>
+        <v>16.80264562282364</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>14.09</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>14.14</v>
+        <v>13.66</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>14.15</v>
+        <v>13.67</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.65</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.672001905442</v>
+        <v>14.15166907441216</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12.50845408176894</v>
+        <v>13.09525884704837</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.38694682734582</v>
+        <v>16.61662627159434</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>459855.0115029219</v>
+        <v>379413.4704905218</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.966806525825302</v>
+        <v>2.447828841874334</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2282.127921667401</v>
+        <v>2376.627921667401</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>2014.381921667401</v>
+        <v>2108.881921667401</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12.50845408176894</v>
+        <v>13.09525884704837</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12.50845408176894</v>
+        <v>13.09525884704837</v>
       </c>
     </row>
     <row r="13">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>9.71790213693812</v>
+        <v>10.00837049575144</v>
       </c>
       <c r="F11" t="n">
-        <v>7.684149733871723</v>
+        <v>7.913829178120249</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16.38694682734582</v>
+        <v>16.61662627159434</v>
       </c>
     </row>
     <row r="13">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.54135818806035</v>
+        <v>10.92509192323648</v>
       </c>
       <c r="C2" t="n">
-        <v>11.8032949875963</v>
+        <v>12.23499543966945</v>
       </c>
       <c r="D2" t="n">
-        <v>13.06523178713226</v>
+        <v>13.54489895610241</v>
       </c>
       <c r="E2" t="n">
-        <v>14.32716858666821</v>
+        <v>14.85480247253538</v>
       </c>
       <c r="F2" t="n">
-        <v>15.58910538620415</v>
+        <v>16.16470598896834</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10.84474324721523</v>
+        <v>11.22847698239135</v>
       </c>
       <c r="C3" t="n">
-        <v>12.10668004675118</v>
+        <v>12.53838049882432</v>
       </c>
       <c r="D3" t="n">
-        <v>13.36861684628713</v>
+        <v>13.84828401525728</v>
       </c>
       <c r="E3" t="n">
-        <v>14.63055364582308</v>
+        <v>15.15818753169025</v>
       </c>
       <c r="F3" t="n">
-        <v>15.89249044535902</v>
+        <v>16.46809104812321</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.1481283063701</v>
+        <v>11.53186204154622</v>
       </c>
       <c r="C4" t="n">
-        <v>12.41006510590605</v>
+        <v>12.84176555797919</v>
       </c>
       <c r="D4" t="n">
-        <v>13.672001905442</v>
+        <v>14.15166907441216</v>
       </c>
       <c r="E4" t="n">
-        <v>14.93393870497795</v>
+        <v>15.46157259084513</v>
       </c>
       <c r="F4" t="n">
-        <v>16.1958755045139</v>
+        <v>16.77147610727809</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.45151336552497</v>
+        <v>11.8352471007011</v>
       </c>
       <c r="C5" t="n">
-        <v>12.71345016506092</v>
+        <v>13.14515061713407</v>
       </c>
       <c r="D5" t="n">
-        <v>13.97538696459687</v>
+        <v>14.45505413356703</v>
       </c>
       <c r="E5" t="n">
-        <v>15.23732376413282</v>
+        <v>15.76495765</v>
       </c>
       <c r="F5" t="n">
-        <v>16.49926056366877</v>
+        <v>17.07486116643296</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11.75489842467984</v>
+        <v>12.13863215985597</v>
       </c>
       <c r="C6" t="n">
-        <v>13.0168352242158</v>
+        <v>13.44853567628894</v>
       </c>
       <c r="D6" t="n">
-        <v>14.27877202375175</v>
+        <v>14.7584391927219</v>
       </c>
       <c r="E6" t="n">
-        <v>15.5407088232877</v>
+        <v>16.06834270915487</v>
       </c>
       <c r="F6" t="n">
-        <v>16.80264562282364</v>
+        <v>17.37824622558783</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>13.61</v>
+        <v>14.09</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>13.66</v>
+        <v>14.14</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>13.67</v>
+        <v>14.15</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.15166907441216</v>
+        <v>14.95433371394532</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.09525884704837</v>
+        <v>13.87628405599766</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16.61662627159434</v>
+        <v>17.4697829158232</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>379413.4704905218</v>
+        <v>310818.3844915639</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.447828841874334</v>
+        <v>2.005279899945574</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2376.627921667401</v>
+        <v>2558.081499854863</v>
       </c>
     </row>
     <row r="3">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>55.676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>2108.881921667401</v>
+        <v>2234.659499854863</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.09525884704837</v>
+        <v>13.87628405599766</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.09525884704837</v>
+        <v>13.87628405599766</v>
       </c>
     </row>
     <row r="13">
@@ -813,13 +813,13 @@
         <v>118981.25</v>
       </c>
       <c r="D2" t="n">
-        <v>1.265221272715406</v>
+        <v>1.325903505677114</v>
       </c>
       <c r="E2" t="n">
-        <v>1.265221272715406</v>
+        <v>1.325903505677114</v>
       </c>
       <c r="F2" t="n">
-        <v>1.232638534942843</v>
+        <v>1.291758042611605</v>
       </c>
     </row>
     <row r="3">
@@ -835,13 +835,13 @@
         <v>138781.25</v>
       </c>
       <c r="D3" t="n">
-        <v>1.506864224159076</v>
+        <v>1.57853022764095</v>
       </c>
       <c r="E3" t="n">
-        <v>1.506864224159076</v>
+        <v>1.57853022764095</v>
       </c>
       <c r="F3" t="n">
-        <v>1.430252226873973</v>
+        <v>1.49827458710242</v>
       </c>
     </row>
     <row r="4">
@@ -857,13 +857,13 @@
         <v>128881.25</v>
       </c>
       <c r="D4" t="n">
-        <v>1.386042748437241</v>
+        <v>1.452216866659032</v>
       </c>
       <c r="E4" t="n">
-        <v>1.386042748437241</v>
+        <v>1.452216866659032</v>
       </c>
       <c r="F4" t="n">
-        <v>1.281694117104788</v>
+        <v>1.34288629759496</v>
       </c>
     </row>
     <row r="5">
@@ -879,13 +879,13 @@
         <v>105781.25</v>
       </c>
       <c r="D5" t="n">
-        <v>1.10412597175296</v>
+        <v>1.157485691034557</v>
       </c>
       <c r="E5" t="n">
-        <v>1.10412597175296</v>
+        <v>1.157485691034557</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9947080826603245</v>
+        <v>1.042779901832934</v>
       </c>
     </row>
     <row r="6">
@@ -901,13 +901,13 @@
         <v>99181.25</v>
       </c>
       <c r="D6" t="n">
-        <v>1.023578321271737</v>
+        <v>1.073276783713278</v>
       </c>
       <c r="E6" t="n">
-        <v>1.023578321271737</v>
+        <v>1.073276783713278</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8983950611276215</v>
+        <v>0.9420154195068838</v>
       </c>
     </row>
     <row r="7">
@@ -923,13 +923,13 @@
         <v>112381.25</v>
       </c>
       <c r="D7" t="n">
-        <v>1.184673622234184</v>
+        <v>1.241694598355835</v>
       </c>
       <c r="E7" t="n">
-        <v>1.184673622234184</v>
+        <v>1.241694598355835</v>
       </c>
       <c r="F7" t="n">
-        <v>1.013011208018604</v>
+        <v>1.061769690371287</v>
       </c>
     </row>
     <row r="8">
@@ -945,13 +945,13 @@
         <v>118981.25</v>
       </c>
       <c r="D8" t="n">
-        <v>1.265221272715406</v>
+        <v>1.325903505677114</v>
       </c>
       <c r="E8" t="n">
-        <v>1.265221272715406</v>
+        <v>1.325903505677114</v>
       </c>
       <c r="F8" t="n">
-        <v>1.054025875057338</v>
+        <v>1.104578806056218</v>
       </c>
     </row>
     <row r="9">
@@ -967,13 +967,13 @@
         <v>95881.25</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9833044960311257</v>
+        <v>1.031172330052639</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9833044960311257</v>
+        <v>1.031172330052639</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7980719876886012</v>
+        <v>0.8369225956112641</v>
       </c>
     </row>
     <row r="10">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.702797093474093</v>
+        <v>9.120985340687573</v>
       </c>
     </row>
     <row r="11">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.00837049575144</v>
+        <v>10.55846132704065</v>
       </c>
       <c r="F11" t="n">
-        <v>7.913829178120249</v>
+        <v>8.348797575135624</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16.61662627159434</v>
+        <v>17.4697829158232</v>
       </c>
     </row>
     <row r="13">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10.92509192323648</v>
+        <v>11.49993078739075</v>
       </c>
       <c r="C2" t="n">
-        <v>12.23499543966945</v>
+        <v>12.90995696155158</v>
       </c>
       <c r="D2" t="n">
-        <v>13.54489895610241</v>
+        <v>14.31998313571241</v>
       </c>
       <c r="E2" t="n">
-        <v>14.85480247253538</v>
+        <v>15.73000930987324</v>
       </c>
       <c r="F2" t="n">
-        <v>16.16470598896834</v>
+        <v>17.14003548403406</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.22847698239135</v>
+        <v>11.8171060765072</v>
       </c>
       <c r="C3" t="n">
-        <v>12.53838049882432</v>
+        <v>13.22713225066803</v>
       </c>
       <c r="D3" t="n">
-        <v>13.84828401525728</v>
+        <v>14.63715842482886</v>
       </c>
       <c r="E3" t="n">
-        <v>15.15818753169025</v>
+        <v>16.04718459898969</v>
       </c>
       <c r="F3" t="n">
-        <v>16.46809104812321</v>
+        <v>17.45721077315052</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.53186204154622</v>
+        <v>12.13428136562366</v>
       </c>
       <c r="C4" t="n">
-        <v>12.84176555797919</v>
+        <v>13.54430753978449</v>
       </c>
       <c r="D4" t="n">
-        <v>14.15166907441216</v>
+        <v>14.95433371394532</v>
       </c>
       <c r="E4" t="n">
-        <v>15.46157259084513</v>
+        <v>16.36435988810615</v>
       </c>
       <c r="F4" t="n">
-        <v>16.77147610727809</v>
+        <v>17.77438606226698</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11.8352471007011</v>
+        <v>12.45145665474012</v>
       </c>
       <c r="C5" t="n">
-        <v>13.14515061713407</v>
+        <v>13.86148282890095</v>
       </c>
       <c r="D5" t="n">
-        <v>14.45505413356703</v>
+        <v>15.27150900306178</v>
       </c>
       <c r="E5" t="n">
-        <v>15.76495765</v>
+        <v>16.68153517722261</v>
       </c>
       <c r="F5" t="n">
-        <v>17.07486116643296</v>
+        <v>18.09156135138344</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.13863215985597</v>
+        <v>12.76863194385658</v>
       </c>
       <c r="C6" t="n">
-        <v>13.44853567628894</v>
+        <v>14.17865811801741</v>
       </c>
       <c r="D6" t="n">
-        <v>14.7584391927219</v>
+        <v>15.58868429217824</v>
       </c>
       <c r="E6" t="n">
-        <v>16.06834270915487</v>
+        <v>16.99871046633907</v>
       </c>
       <c r="F6" t="n">
-        <v>17.37824622558783</v>
+        <v>18.4087366404999</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>14.09</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>14.14</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>14.15</v>
+        <v>14.95</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.08</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>310818.3844915639</v>
+        <v>260972.1305666721</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.005279899945574</v>
+        <v>1.683691164946271</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.4</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>260972.1305666721</v>
+        <v>270501.561464078</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.683691164946271</v>
+        <v>1.745171364284374</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -1264,7 +1264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.53</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>270501.561464078</v>
+        <v>318148.715951107</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.745171364284374</v>
+        <v>2.052572360974884</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.18</v>
+        <v>16.93</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>318148.715951107</v>
+        <v>299822.8873022496</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.052572360974884</v>
+        <v>1.934341208401611</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16.93</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>299822.8873022496</v>
+        <v>360664.6384164562</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.934341208401611</v>
+        <v>2.326868634944879</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.76</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>360664.6384164562</v>
+        <v>327678.1468485129</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.326868634944879</v>
+        <v>2.114052560312986</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.31</v>
+        <v>18.18</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>327678.1468485129</v>
+        <v>391452.0305465364</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.114052560312986</v>
+        <v>2.525496971267977</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.18</v>
+        <v>17.41</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>391452.0305465364</v>
+        <v>335008.4783080558</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.525496971267977</v>
+        <v>2.161345021342296</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.95433371394532</v>
+        <v>14.68444199560228</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.87628405599766</v>
+        <v>13.58430188596645</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.4697829158232</v>
+        <v>17.25143558475254</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>335008.4783080558</v>
+        <v>354792.4358444569</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.161345021342296</v>
+        <v>2.288983457061012</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2558.081499854863</v>
+        <v>2511.060213218225</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>2234.659499854863</v>
+        <v>2187.638213218225</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.87628405599766</v>
+        <v>13.58430188596645</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.87628405599766</v>
+        <v>13.58430188596645</v>
       </c>
     </row>
     <row r="13">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.55846132704065</v>
+        <v>10.28232433483017</v>
       </c>
       <c r="F11" t="n">
-        <v>8.348797575135624</v>
+        <v>8.130450244064965</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17.4697829158232</v>
+        <v>17.25143558475254</v>
       </c>
     </row>
     <row r="13">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.49993078739075</v>
+        <v>11.28401741271631</v>
       </c>
       <c r="C2" t="n">
-        <v>12.90995696155158</v>
+        <v>12.66705441504283</v>
       </c>
       <c r="D2" t="n">
-        <v>14.31998313571241</v>
+        <v>14.05009141736936</v>
       </c>
       <c r="E2" t="n">
-        <v>15.73000930987324</v>
+        <v>15.43312841969588</v>
       </c>
       <c r="F2" t="n">
-        <v>17.14003548403406</v>
+        <v>16.81616542202241</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.8171060765072</v>
+        <v>11.60119270183277</v>
       </c>
       <c r="C3" t="n">
-        <v>13.22713225066803</v>
+        <v>12.98422970415929</v>
       </c>
       <c r="D3" t="n">
-        <v>14.63715842482886</v>
+        <v>14.36726670648582</v>
       </c>
       <c r="E3" t="n">
-        <v>16.04718459898969</v>
+        <v>15.75030370881234</v>
       </c>
       <c r="F3" t="n">
-        <v>17.45721077315052</v>
+        <v>17.13334071113886</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.13428136562366</v>
+        <v>11.91836799094922</v>
       </c>
       <c r="C4" t="n">
-        <v>13.54430753978449</v>
+        <v>13.30140499327575</v>
       </c>
       <c r="D4" t="n">
-        <v>14.95433371394532</v>
+        <v>14.68444199560228</v>
       </c>
       <c r="E4" t="n">
-        <v>16.36435988810615</v>
+        <v>16.0674789979288</v>
       </c>
       <c r="F4" t="n">
-        <v>17.77438606226698</v>
+        <v>17.45051600025532</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.45145665474012</v>
+        <v>12.23554328006568</v>
       </c>
       <c r="C5" t="n">
-        <v>13.86148282890095</v>
+        <v>13.61858028239221</v>
       </c>
       <c r="D5" t="n">
-        <v>15.27150900306178</v>
+        <v>15.00161728471874</v>
       </c>
       <c r="E5" t="n">
-        <v>16.68153517722261</v>
+        <v>16.38465428704526</v>
       </c>
       <c r="F5" t="n">
-        <v>18.09156135138344</v>
+        <v>17.76769128937178</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.76863194385658</v>
+        <v>12.55271856918214</v>
       </c>
       <c r="C6" t="n">
-        <v>14.17865811801741</v>
+        <v>13.93575557150866</v>
       </c>
       <c r="D6" t="n">
-        <v>15.58868429217824</v>
+        <v>15.3187925738352</v>
       </c>
       <c r="E6" t="n">
-        <v>16.99871046633907</v>
+        <v>16.70182957616172</v>
       </c>
       <c r="F6" t="n">
-        <v>18.4087366404999</v>
+        <v>18.08486657848824</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>14.89</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>14.94</v>
+        <v>14.67</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>14.95</v>
+        <v>14.68</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.41</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>354792.4358444569</v>
+        <v>389978.0268502629</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.288983457061012</v>
+        <v>2.515987270001697</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.89</v>
+        <v>18.45</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>389978.0268502629</v>
+        <v>431027.8830237035</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.515987270001697</v>
+        <v>2.780825051765829</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.45</v>
+        <v>18.665</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>431027.8830237035</v>
+        <v>446788.0956617207</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.780825051765829</v>
+        <v>2.882503842978843</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.665</v>
+        <v>18.76</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>446788.0956617207</v>
+        <v>453751.9105482869</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.882503842978843</v>
+        <v>2.92743168095669</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.68444199560228</v>
+        <v>14.91256354966256</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.58430188596645</v>
+        <v>13.82608624926936</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.25143558475254</v>
+        <v>17.44767725058001</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>453751.9105482869</v>
+        <v>437369.4817624455</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.92743168095669</v>
+        <v>2.821738592015778</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2511.060213218225</v>
+        <v>2443.258938748367</v>
       </c>
     </row>
     <row r="3">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>126.246</v>
+        <v>161.683</v>
       </c>
     </row>
     <row r="4">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>134.146</v>
+        <v>137.59</v>
       </c>
     </row>
     <row r="5">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-505.343</v>
+        <v>-434.804</v>
       </c>
     </row>
     <row r="6">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>2187.638213218225</v>
+        <v>2229.256938748367</v>
       </c>
     </row>
     <row r="10">
@@ -713,7 +713,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161041637</v>
+        <v>161235573</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.58430188596645</v>
+        <v>13.82608624926936</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.58430188596645</v>
+        <v>13.82608624926936</v>
       </c>
     </row>
     <row r="13">
@@ -813,13 +813,13 @@
         <v>118981.25</v>
       </c>
       <c r="D2" t="n">
-        <v>1.325903505677114</v>
+        <v>1.324308693704219</v>
       </c>
       <c r="E2" t="n">
-        <v>1.325903505677114</v>
+        <v>1.324308693704219</v>
       </c>
       <c r="F2" t="n">
-        <v>1.291758042611605</v>
+        <v>1.290204301194058</v>
       </c>
     </row>
     <row r="3">
@@ -835,13 +835,13 @@
         <v>138781.25</v>
       </c>
       <c r="D3" t="n">
-        <v>1.57853022764095</v>
+        <v>1.576631553343884</v>
       </c>
       <c r="E3" t="n">
-        <v>1.57853022764095</v>
+        <v>1.576631553343884</v>
       </c>
       <c r="F3" t="n">
-        <v>1.49827458710242</v>
+        <v>1.496472445212031</v>
       </c>
     </row>
     <row r="4">
@@ -857,13 +857,13 @@
         <v>128881.25</v>
       </c>
       <c r="D4" t="n">
-        <v>1.452216866659032</v>
+        <v>1.450470123524052</v>
       </c>
       <c r="E4" t="n">
-        <v>1.452216866659032</v>
+        <v>1.450470123524052</v>
       </c>
       <c r="F4" t="n">
-        <v>1.34288629759496</v>
+        <v>1.341271058524794</v>
       </c>
     </row>
     <row r="5">
@@ -879,13 +879,13 @@
         <v>105781.25</v>
       </c>
       <c r="D5" t="n">
-        <v>1.157485691034557</v>
+        <v>1.156093453944442</v>
       </c>
       <c r="E5" t="n">
-        <v>1.157485691034557</v>
+        <v>1.156093453944442</v>
       </c>
       <c r="F5" t="n">
-        <v>1.042779901832934</v>
+        <v>1.041525634184182</v>
       </c>
     </row>
     <row r="6">
@@ -901,13 +901,13 @@
         <v>99181.25</v>
       </c>
       <c r="D6" t="n">
-        <v>1.073276783713278</v>
+        <v>1.071985834064554</v>
       </c>
       <c r="E6" t="n">
-        <v>1.073276783713278</v>
+        <v>1.071985834064554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9420154195068838</v>
+        <v>0.9408823525353819</v>
       </c>
     </row>
     <row r="7">
@@ -923,13 +923,13 @@
         <v>112381.25</v>
       </c>
       <c r="D7" t="n">
-        <v>1.241694598355835</v>
+        <v>1.240201073824331</v>
       </c>
       <c r="E7" t="n">
-        <v>1.241694598355835</v>
+        <v>1.240201073824331</v>
       </c>
       <c r="F7" t="n">
-        <v>1.061769690371287</v>
+        <v>1.060492581586665</v>
       </c>
     </row>
     <row r="8">
@@ -945,13 +945,13 @@
         <v>118981.25</v>
       </c>
       <c r="D8" t="n">
-        <v>1.325903505677114</v>
+        <v>1.324308693704219</v>
       </c>
       <c r="E8" t="n">
-        <v>1.325903505677114</v>
+        <v>1.324308693704219</v>
       </c>
       <c r="F8" t="n">
-        <v>1.104578806056218</v>
+        <v>1.103250205975321</v>
       </c>
     </row>
     <row r="9">
@@ -967,13 +967,13 @@
         <v>95881.25</v>
       </c>
       <c r="D9" t="n">
-        <v>1.031172330052639</v>
+        <v>1.029932024124609</v>
       </c>
       <c r="E9" t="n">
-        <v>1.031172330052639</v>
+        <v>1.029932024124609</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8369225956112641</v>
+        <v>0.8359159354959901</v>
       </c>
     </row>
     <row r="10">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9.120985340687573</v>
+        <v>9.110014514708421</v>
       </c>
     </row>
     <row r="11">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.28232433483017</v>
+        <v>10.544379446543</v>
       </c>
       <c r="F11" t="n">
-        <v>8.130450244064965</v>
+        <v>8.337662735871589</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17.25143558475254</v>
+        <v>17.44767725058001</v>
       </c>
     </row>
     <row r="13">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.28401741271631</v>
+        <v>11.59427764136111</v>
       </c>
       <c r="C2" t="n">
-        <v>12.66705441504283</v>
+        <v>12.93662680847786</v>
       </c>
       <c r="D2" t="n">
-        <v>14.05009141736936</v>
+        <v>14.27897597559461</v>
       </c>
       <c r="E2" t="n">
-        <v>15.43312841969588</v>
+        <v>15.62132514271136</v>
       </c>
       <c r="F2" t="n">
-        <v>16.81616542202241</v>
+        <v>16.96367430982811</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.60119270183277</v>
+        <v>11.91107142839508</v>
       </c>
       <c r="C3" t="n">
-        <v>12.98422970415929</v>
+        <v>13.25342059551183</v>
       </c>
       <c r="D3" t="n">
-        <v>14.36726670648582</v>
+        <v>14.59576976262858</v>
       </c>
       <c r="E3" t="n">
-        <v>15.75030370881234</v>
+        <v>15.93811892974533</v>
       </c>
       <c r="F3" t="n">
-        <v>17.13334071113886</v>
+        <v>17.28046809686209</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.91836799094922</v>
+        <v>12.22786521542906</v>
       </c>
       <c r="C4" t="n">
-        <v>13.30140499327575</v>
+        <v>13.5702143825458</v>
       </c>
       <c r="D4" t="n">
-        <v>14.68444199560228</v>
+        <v>14.91256354966256</v>
       </c>
       <c r="E4" t="n">
-        <v>16.0674789979288</v>
+        <v>16.25491271677931</v>
       </c>
       <c r="F4" t="n">
-        <v>17.45051600025532</v>
+        <v>17.59726188389606</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.23554328006568</v>
+        <v>12.54465900246303</v>
       </c>
       <c r="C5" t="n">
-        <v>13.61858028239221</v>
+        <v>13.88700816957978</v>
       </c>
       <c r="D5" t="n">
-        <v>15.00161728471874</v>
+        <v>15.22935733669653</v>
       </c>
       <c r="E5" t="n">
-        <v>16.38465428704526</v>
+        <v>16.57170650381328</v>
       </c>
       <c r="F5" t="n">
-        <v>17.76769128937178</v>
+        <v>17.91405567093003</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.55271856918214</v>
+        <v>12.861452789497</v>
       </c>
       <c r="C6" t="n">
-        <v>13.93575557150866</v>
+        <v>14.20380195661375</v>
       </c>
       <c r="D6" t="n">
-        <v>15.3187925738352</v>
+        <v>15.5461511237305</v>
       </c>
       <c r="E6" t="n">
-        <v>16.70182957616172</v>
+        <v>16.88850029084725</v>
       </c>
       <c r="F6" t="n">
-        <v>18.08486657848824</v>
+        <v>18.23084945796401</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>14.62</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>14.67</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>14.68</v>
+        <v>14.91</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.91256354966256</v>
+        <v>15.98438742898056</v>
       </c>
     </row>
     <row r="6">
@@ -502,7 +502,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13.82608624926936</v>
+        <v>15.00542108117422</v>
       </c>
     </row>
     <row r="8">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17.44767725058001</v>
+        <v>18.26864224052869</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>437369.4817624455</v>
+        <v>358706.6221544342</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.821738592015778</v>
+        <v>2.314236271964091</v>
       </c>
     </row>
   </sheetData>
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2443.258938748367</v>
+        <v>2633.409666129406</v>
       </c>
     </row>
     <row r="3">
@@ -703,7 +703,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>2229.256938748367</v>
+        <v>2419.407666129406</v>
       </c>
     </row>
     <row r="10">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13.82608624926936</v>
+        <v>15.00542108117422</v>
       </c>
     </row>
     <row r="12">
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13.82608624926936</v>
+        <v>15.00542108117422</v>
       </c>
     </row>
     <row r="13">
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>10.544379446543</v>
+        <v>11.58262801098812</v>
       </c>
       <c r="F11" t="n">
-        <v>8.337662735871589</v>
+        <v>9.158627725820269</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>17.44767725058001</v>
+        <v>18.26864224052869</v>
       </c>
     </row>
     <row r="13">
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.59427764136111</v>
+        <v>12.45173674481551</v>
       </c>
       <c r="C2" t="n">
-        <v>12.93662680847786</v>
+        <v>13.90126829986406</v>
       </c>
       <c r="D2" t="n">
-        <v>14.27897597559461</v>
+        <v>15.35079985491262</v>
       </c>
       <c r="E2" t="n">
-        <v>15.62132514271136</v>
+        <v>16.80033140996117</v>
       </c>
       <c r="F2" t="n">
-        <v>16.96367430982811</v>
+        <v>18.24986296500972</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11.91107142839508</v>
+        <v>12.76853053184948</v>
       </c>
       <c r="C3" t="n">
-        <v>13.25342059551183</v>
+        <v>14.21806208689803</v>
       </c>
       <c r="D3" t="n">
-        <v>14.59576976262858</v>
+        <v>15.66759364194659</v>
       </c>
       <c r="E3" t="n">
-        <v>15.93811892974533</v>
+        <v>17.11712519699515</v>
       </c>
       <c r="F3" t="n">
-        <v>17.28046809686209</v>
+        <v>18.56665675204369</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.22786521542906</v>
+        <v>13.08532431888345</v>
       </c>
       <c r="C4" t="n">
-        <v>13.5702143825458</v>
+        <v>14.53485587393201</v>
       </c>
       <c r="D4" t="n">
-        <v>14.91256354966256</v>
+        <v>15.98438742898056</v>
       </c>
       <c r="E4" t="n">
-        <v>16.25491271677931</v>
+        <v>17.43391898402912</v>
       </c>
       <c r="F4" t="n">
-        <v>17.59726188389606</v>
+        <v>18.88345053907766</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12.54465900246303</v>
+        <v>13.40211810591743</v>
       </c>
       <c r="C5" t="n">
-        <v>13.88700816957978</v>
+        <v>14.85164966096598</v>
       </c>
       <c r="D5" t="n">
-        <v>15.22935733669653</v>
+        <v>16.30118121601453</v>
       </c>
       <c r="E5" t="n">
-        <v>16.57170650381328</v>
+        <v>17.75071277106309</v>
       </c>
       <c r="F5" t="n">
-        <v>17.91405567093003</v>
+        <v>19.20024432611164</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12.861452789497</v>
+        <v>13.7189118929514</v>
       </c>
       <c r="C6" t="n">
-        <v>14.20380195661375</v>
+        <v>15.16844344799995</v>
       </c>
       <c r="D6" t="n">
-        <v>15.5461511237305</v>
+        <v>16.61797500304851</v>
       </c>
       <c r="E6" t="n">
-        <v>16.88850029084725</v>
+        <v>18.06750655809707</v>
       </c>
       <c r="F6" t="n">
-        <v>18.23084945796401</v>
+        <v>19.51703811314561</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>14.85</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>14.9</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>14.91</v>
+        <v>15.98</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.98438742898056</v>
+        <v>15.31587504438778</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18.26864224052869</v>
+        <v>16.04026762521943</v>
       </c>
     </row>
     <row r="9">
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111500</v>
+        <v>105700</v>
       </c>
     </row>
     <row r="10">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>155000</v>
+        <v>142675</v>
       </c>
     </row>
     <row r="11">
@@ -542,7 +542,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7875</v>
+        <v>2.6425</v>
       </c>
     </row>
     <row r="12">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>358706.6221544342</v>
+        <v>494031.4073282281</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.314236271964091</v>
+        <v>3.462634710553552</v>
       </c>
     </row>
   </sheetData>
@@ -807,19 +807,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>147500</v>
+        <v>179650</v>
       </c>
       <c r="C2" t="n">
-        <v>118981.25</v>
+        <v>132922</v>
       </c>
       <c r="D2" t="n">
-        <v>1.324308693704219</v>
+        <v>1.501963739437636</v>
       </c>
       <c r="E2" t="n">
-        <v>1.324308693704219</v>
+        <v>1.501963739437636</v>
       </c>
       <c r="F2" t="n">
-        <v>1.290204301194058</v>
+        <v>1.463284267537069</v>
       </c>
     </row>
     <row r="3">
@@ -829,19 +829,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>183500</v>
+        <v>179650</v>
       </c>
       <c r="C3" t="n">
-        <v>138781.25</v>
+        <v>132922</v>
       </c>
       <c r="D3" t="n">
-        <v>1.576631553343884</v>
+        <v>1.501963739437636</v>
       </c>
       <c r="E3" t="n">
-        <v>1.576631553343884</v>
+        <v>1.501963739437636</v>
       </c>
       <c r="F3" t="n">
-        <v>1.496472445212031</v>
+        <v>1.425600892617556</v>
       </c>
     </row>
     <row r="4">
@@ -851,19 +851,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>165500</v>
+        <v>105700</v>
       </c>
       <c r="C4" t="n">
-        <v>128881.25</v>
+        <v>94468</v>
       </c>
       <c r="D4" t="n">
-        <v>1.450470123524052</v>
+        <v>1.011922161428359</v>
       </c>
       <c r="E4" t="n">
-        <v>1.450470123524052</v>
+        <v>1.011922161428359</v>
       </c>
       <c r="F4" t="n">
-        <v>1.341271058524794</v>
+        <v>0.9357393072710236</v>
       </c>
     </row>
     <row r="5">
@@ -873,19 +873,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>123500</v>
+        <v>105700</v>
       </c>
       <c r="C5" t="n">
-        <v>105781.25</v>
+        <v>94468</v>
       </c>
       <c r="D5" t="n">
-        <v>1.156093453944442</v>
+        <v>1.011922161428359</v>
       </c>
       <c r="E5" t="n">
-        <v>1.156093453944442</v>
+        <v>1.011922161428359</v>
       </c>
       <c r="F5" t="n">
-        <v>1.041525634184182</v>
+        <v>0.9116415868723955</v>
       </c>
     </row>
     <row r="6">
@@ -895,19 +895,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111500</v>
+        <v>48850</v>
       </c>
       <c r="C6" t="n">
-        <v>99181.25</v>
+        <v>64906</v>
       </c>
       <c r="D6" t="n">
-        <v>1.071985834064554</v>
+        <v>0.6351964858390772</v>
       </c>
       <c r="E6" t="n">
-        <v>1.071985834064554</v>
+        <v>0.6351964858390772</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9408823525353819</v>
+        <v>0.557512184328444</v>
       </c>
     </row>
     <row r="7">
@@ -917,19 +917,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>135500</v>
+        <v>48850</v>
       </c>
       <c r="C7" t="n">
-        <v>112381.25</v>
+        <v>64906</v>
       </c>
       <c r="D7" t="n">
-        <v>1.240201073824331</v>
+        <v>0.6351964858390772</v>
       </c>
       <c r="E7" t="n">
-        <v>1.240201073824331</v>
+        <v>0.6351964858390772</v>
       </c>
       <c r="F7" t="n">
-        <v>1.060492581586665</v>
+        <v>0.5431547958631072</v>
       </c>
     </row>
     <row r="8">
@@ -939,19 +939,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>147500</v>
+        <v>48850</v>
       </c>
       <c r="C8" t="n">
-        <v>118981.25</v>
+        <v>64906</v>
       </c>
       <c r="D8" t="n">
-        <v>1.324308693704219</v>
+        <v>0.6351964858390772</v>
       </c>
       <c r="E8" t="n">
-        <v>1.324308693704219</v>
+        <v>0.6351964858390772</v>
       </c>
       <c r="F8" t="n">
-        <v>1.103250205975321</v>
+        <v>0.5291671474847837</v>
       </c>
     </row>
     <row r="9">
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105500</v>
+        <v>48850</v>
       </c>
       <c r="C9" t="n">
-        <v>95881.25</v>
+        <v>64906</v>
       </c>
       <c r="D9" t="n">
-        <v>1.029932024124609</v>
+        <v>0.6351964858390772</v>
       </c>
       <c r="E9" t="n">
-        <v>1.029932024124609</v>
+        <v>0.6351964858390772</v>
       </c>
       <c r="F9" t="n">
-        <v>0.8359159354959901</v>
+        <v>0.5155397174247845</v>
       </c>
     </row>
     <row r="10">
@@ -983,7 +983,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>9.110014514708421</v>
+        <v>6.881639899399164</v>
       </c>
     </row>
     <row r="11">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18.26864224052869</v>
+        <v>16.04026762521943</v>
       </c>
     </row>
     <row r="13">
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>155000</v>
+        <v>142675</v>
       </c>
     </row>
   </sheetData>
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12.45173674481551</v>
+        <v>11.99724605947548</v>
       </c>
       <c r="C2" t="n">
-        <v>13.90126829986406</v>
+        <v>13.44677761452403</v>
       </c>
       <c r="D2" t="n">
-        <v>15.35079985491262</v>
+        <v>14.89630916957259</v>
       </c>
       <c r="E2" t="n">
-        <v>16.80033140996117</v>
+        <v>16.34584072462115</v>
       </c>
       <c r="F2" t="n">
-        <v>18.24986296500972</v>
+        <v>17.79537227966969</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12.76853053184948</v>
+        <v>12.20702899688308</v>
       </c>
       <c r="C3" t="n">
-        <v>14.21806208689803</v>
+        <v>13.65656055193163</v>
       </c>
       <c r="D3" t="n">
-        <v>15.66759364194659</v>
+        <v>15.10609210698019</v>
       </c>
       <c r="E3" t="n">
-        <v>17.11712519699515</v>
+        <v>16.55562366202874</v>
       </c>
       <c r="F3" t="n">
-        <v>18.56665675204369</v>
+        <v>18.00515521707729</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13.08532431888345</v>
+        <v>12.41681193429068</v>
       </c>
       <c r="C4" t="n">
-        <v>14.53485587393201</v>
+        <v>13.86634348933923</v>
       </c>
       <c r="D4" t="n">
-        <v>15.98438742898056</v>
+        <v>15.31587504438778</v>
       </c>
       <c r="E4" t="n">
-        <v>17.43391898402912</v>
+        <v>16.76540659943634</v>
       </c>
       <c r="F4" t="n">
-        <v>18.88345053907766</v>
+        <v>18.21493815448489</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13.40211810591743</v>
+        <v>12.62659487169827</v>
       </c>
       <c r="C5" t="n">
-        <v>14.85164966096598</v>
+        <v>14.07612642674682</v>
       </c>
       <c r="D5" t="n">
-        <v>16.30118121601453</v>
+        <v>15.52565798179538</v>
       </c>
       <c r="E5" t="n">
-        <v>17.75071277106309</v>
+        <v>16.97518953684394</v>
       </c>
       <c r="F5" t="n">
-        <v>19.20024432611164</v>
+        <v>18.42472109189249</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13.7189118929514</v>
+        <v>12.83637780910587</v>
       </c>
       <c r="C6" t="n">
-        <v>15.16844344799995</v>
+        <v>14.28590936415442</v>
       </c>
       <c r="D6" t="n">
-        <v>16.61797500304851</v>
+        <v>15.73544091920298</v>
       </c>
       <c r="E6" t="n">
-        <v>18.06750655809707</v>
+        <v>17.18497247425154</v>
       </c>
       <c r="F6" t="n">
-        <v>19.51703811314561</v>
+        <v>18.63450402930008</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>15.92</v>
+        <v>15.26</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>15.97</v>
+        <v>15.3</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>15.98</v>
+        <v>15.32</v>
       </c>
     </row>
   </sheetData>
@@ -1264,7 +1264,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>spot TCE VLCC: $285,500/day is 7.1x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
+          <t>spot TCE VLCC: $488,900/day is 12.2x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
         </is>
       </c>
     </row>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.76</v>
+        <v>18.72</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>494031.4073282281</v>
+        <v>489950.7608725212</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.462634710553552</v>
+        <v>3.4340337190995</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.72</v>
+        <v>19.52</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>489950.7608725212</v>
+        <v>571563.6899866502</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.4340337190995</v>
+        <v>4.006053548180482</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.52</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>571563.6899866502</v>
+        <v>535858.0334992189</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.006053548180482</v>
+        <v>3.755794872957553</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/dht_fv_report.xlsx
+++ b/outputs/dht_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19.17</v>
+        <v>19.66</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>535858.0334992189</v>
+        <v>585845.9525816231</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.755794872957553</v>
+        <v>4.106157018269656</v>
       </c>
     </row>
   </sheetData>
